--- a/data/gravel/Binary SuperB XC 2025.xlsx
+++ b/data/gravel/Binary SuperB XC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2921F462-8F24-EF4F-A0A1-A9E733A3D443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D626B383-F7C5-CB44-B58A-B38746683553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="1020" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>SuperB XC</t>
+  </si>
+  <si>
+    <t>https://binarybicycles.com/wp-content/uploads/2022/01/binary-superb-xc-mtb-frame.jpg</t>
   </si>
 </sst>
 </file>
@@ -783,6 +786,11 @@
         <v>103</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -1703,6 +1711,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{B42B96D1-8655-E24E-A839-A5C00DFAAB8E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/Binary SuperB XC 2025.xlsx
+++ b/data/gravel/Binary SuperB XC 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D626B383-F7C5-CB44-B58A-B38746683553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563FC53-FE9E-7748-A7BF-0BE5A13618C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="1020" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>https://binarybicycles.com/wp-content/uploads/2022/01/binary-superb-xc-mtb-frame.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Casa Grande, Arizona, USA</t>
   </si>
 </sst>
 </file>
@@ -740,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1710,6 +1716,14 @@
         <v>84</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{B42B96D1-8655-E24E-A839-A5C00DFAAB8E}"/>

--- a/data/gravel/Binary SuperB XC 2025.xlsx
+++ b/data/gravel/Binary SuperB XC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563FC53-FE9E-7748-A7BF-0BE5A13618C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C6F39F-D60A-BA45-B0E1-78355D065136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="1020" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,24 @@
   </si>
   <si>
     <t>Casa Grande, Arizona, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -746,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1563,164 +1581,194 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B69">
-        <v>2099</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75">
+        <v>2099</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>110</v>
       </c>
     </row>

--- a/data/gravel/Binary SuperB XC 2025.xlsx
+++ b/data/gravel/Binary SuperB XC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C6F39F-D60A-BA45-B0E1-78355D065136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D732DFE-C86F-6647-8CAB-13FBF9C11EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="1020" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -86,9 +86,6 @@
     <t>fork_offset_rake</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>wheelbase</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -353,9 +347,6 @@
     <t>435-450</t>
   </si>
   <si>
-    <t>a8:f32</t>
-  </si>
-  <si>
     <t>SuperB XC</t>
   </si>
   <si>
@@ -384,6 +375,24 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Dimensions are using an unsagged 100mm fork and 29 x 2.6 wheels and tires</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>100-120</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -393,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -434,6 +443,12 @@
       <color rgb="FF313131"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFC77C56"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -456,7 +471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -467,6 +482,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -764,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -775,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -783,7 +799,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -807,12 +823,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -820,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -828,19 +844,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -859,12 +875,12 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="6">
         <v>586</v>
@@ -878,7 +894,9 @@
       <c r="F9" s="6">
         <v>652</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="10" t="s">
+        <v>114</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -894,7 +912,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C10" s="6">
         <v>395</v>
@@ -929,7 +947,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="6">
         <v>74.5</v>
@@ -964,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6">
         <v>100</v>
@@ -1000,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="6">
         <v>69</v>
@@ -1035,7 +1053,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -1068,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <f>VALUE(LEFT(H15,3))</f>
@@ -1087,19 +1105,19 @@
         <v>435</v>
       </c>
       <c r="H15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -1107,10 +1125,10 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16">
         <v>505</v>
@@ -1134,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C17">
         <v>51</v>
@@ -1157,10 +1175,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>1100</v>
@@ -1182,10 +1200,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>599</v>
@@ -1202,10 +1220,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>417</v>
@@ -1222,10 +1240,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>682</v>
@@ -1242,10 +1260,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>776</v>
@@ -1262,20 +1280,39 @@
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="A23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -1283,8 +1320,8 @@
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
@@ -1306,7 +1343,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
@@ -1317,20 +1354,9 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I28" s="2"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -1339,19 +1365,19 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="F29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -1361,7 +1387,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>2.6</v>
@@ -1383,15 +1409,20 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>2.6</v>
+      </c>
+      <c r="D31">
+        <v>2.6</v>
+      </c>
+      <c r="E31">
+        <v>2.6</v>
+      </c>
+      <c r="F31">
+        <v>2.6</v>
+      </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -1400,7 +1431,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -1410,51 +1441,53 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
       <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="J33" s="7"/>
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="F35" s="1"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>97</v>
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1466,10 +1499,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1481,10 +1514,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -1496,9 +1529,11 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1509,21 +1544,23 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1">
-        <v>15</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41">
-        <v>2.6</v>
+        <v>34</v>
+      </c>
+      <c r="B41" s="1">
+        <v>15</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1531,7 +1568,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="B42">
+        <v>2.6</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1539,10 +1579,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1550,226 +1587,237 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B48">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>42</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>54</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="1"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>64</v>
-      </c>
-      <c r="B75">
-        <v>2099</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>92</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>2099</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>67</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B79" t="s">
-        <v>110</v>
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
